--- a/Stokvel_19072026.xlsx
+++ b/Stokvel_19072026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livenmmuac-my.sharepoint.com/personal/nkululekon_mandela_ac_za/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NKULULEKON\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{7EE71161-40B8-409F-A9F0-B94FC2847653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EE16B03-E2D4-4B64-BFBB-73B09C9BBB5F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625F5CEB-F28E-4A7D-A36B-4FCF99BAF67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{F7718169-9FE6-4991-8BE7-5A2861BD5E41}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F7718169-9FE6-4991-8BE7-5A2861BD5E41}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Names</t>
   </si>
@@ -99,13 +99,16 @@
   </si>
   <si>
     <t>Sandile Ngenya</t>
+  </si>
+  <si>
+    <t>Profit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,24 +481,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D2EBDDB-99E8-4061-93AF-315D39FCA812}">
   <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1328125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" customWidth="1"/>
+    <col min="8" max="9" width="6.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.3984375" customWidth="1"/>
     <col min="21" max="21" width="9" customWidth="1"/>
-    <col min="22" max="22" width="10.42578125" customWidth="1"/>
-    <col min="23" max="23" width="10.5703125" customWidth="1"/>
+    <col min="22" max="22" width="10.3984375" customWidth="1"/>
+    <col min="23" max="23" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -536,7 +539,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -562,11 +565,11 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <f t="shared" ref="M2:M8" si="0">SUM(B2:L2)</f>
+        <f t="shared" ref="M2:M10" si="0">SUM(B2:L2)</f>
         <v>9000</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -596,7 +599,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -626,7 +629,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -656,7 +659,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -689,7 +692,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -719,7 +722,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -749,7 +752,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -778,11 +781,41 @@
         <v>43250</v>
       </c>
       <c r="M9">
-        <f>SUM(B9:L9)</f>
+        <f t="shared" si="0"/>
         <v>5750</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>7000</v>
+      </c>
+      <c r="C10">
+        <v>7000</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.45">
       <c r="U12" s="1"/>
     </row>
   </sheetData>
